--- a/練習用ファイル.xlsx
+++ b/練習用ファイル.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maedat5\projects\excel-practice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3F3E2A61-D289-498F-8FD4-7FDE8F1CBD5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AA69A37-F33B-4170-BEB5-BA31E1AE2720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{66A835F0-D663-4650-A63B-AB44E4808F46}"/>
   </bookViews>
@@ -33,6 +33,15 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+  <si>
+    <t>qqqqq</t>
+    <phoneticPr fontId="1"/>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -416,7 +425,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{301BB5C8-18D7-4789-A2D3-4178DB4757AD}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
